--- a/docs/testcases/manzil-web-testcases.xlsx
+++ b/docs/testcases/manzil-web-testcases.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>По умолчанию выбрана страна Китай, показан код +86. В списке доступны ровно 5 стран: Китай, Узбекистан, Россия, Кыргызстан, Таджикистан. Других стран в списке нет.</t>
+          <t>По умолчанию выбрана страна Китай, код +86. В пикере РОВНО 5 стран (коды набора +86 CN, +998 UZ, +7 RU, +996 KG, +992 TJ), других нет. Уточнено по факту: имена стран отображаются в англ. формате + ISO + код («ChinaCN (+86)», «UzbekistanUZ (+998)») — стандартный react-phone-number-input, НЕ локализованы (низкий приоритет i18n).</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
@@ -1091,7 +1091,7 @@
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>web|positive</t>
+          <t>web|positive · уточнено по факту 2026-07-24: пикер — MUI Menu, имена стран англ.+ISO+код, проверка по кодам набора (язык-независимо); имена не локализованы — низкий-pri i18n</t>
         </is>
       </c>
     </row>

--- a/docs/testcases/manzil-web-testcases.xlsx
+++ b/docs/testcases/manzil-web-testcases.xlsx
@@ -1091,7 +1091,7 @@
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>web|positive · уточнено по факту 2026-07-24: пикер — MUI Menu, имена стран англ.+ISO+код, проверка по кодам набора (язык-независимо); имена не локализованы — низкий-pri i18n</t>
+          <t>web|positive · уточнено по факту 2026-07-24: пикер — MUI Menu, имена стран англ.+ISO+код, проверка по кодам набора (язык-независимо); имена не локализованы — низкий-pri i18n (→ BUG-041: имена стран не локализованы)</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Список фильтруется по мере ввода — остаются только подходящие страны. После очистки поиска снова показаны все 5 поддерживаемых стран.</t>
+          <t>Пикер страны — MUI Menu из 5 стран БЕЗ поля поиска (короткий список, фильтрация не предусмотрена). Уточнено по факту 2026-07-24: кейс описывал несуществующую фильтрацию; тест проверяет отсутствие search-input + ровно 5 стран.</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr">
@@ -1140,7 +1140,7 @@
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>web|positive</t>
+          <t>web|positive · уточнено по факту: поиска в пикере нет (5 стран)</t>
         </is>
       </c>
     </row>

--- a/docs/testcases/manzil-web-testcases.xlsx
+++ b/docs/testcases/manzil-web-testcases.xlsx
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>370</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Вход в веб не выполняется: появляется всплывающее сообщение «Эта учётная запись не поддерживается», пользователь остаётся на странице входа. Сессия не создаётся — после обновления страницы (F5) по-прежнему открыта форма входа.</t>
+          <t>Вход в веб не выполняется: тост «У вас нет доступа к этому приложению» (уточнено по факту 2026-07-24; прежний текст «Эта учётная запись не поддерживается» устарел), пользователь остаётся на /auth/login, сессии нет.</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -1830,7 +1830,7 @@
       <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>web|rbac</t>
+          <t>web|rbac · уточнено по факту: тост «У вас нет доступа к этому приложению»</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7131,6 +7131,354 @@
       <c r="J65" s="2" t="inlineStr">
         <is>
           <t>web|a11y</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>WEB-SA-066</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Web — Супер-администратор</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>/super-admin/partners/drivers</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Вкладки статуса проверки в списке водителей</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Вход под Супер-админом. На стенде есть самозарегистрированные водители в статусах «на рассмотрении», «проверен» и «отклонён» (создаются регистрацией через мобильный API + решением админа).</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>1. Открыть «Партнёры → Водители».
+2. Осмотреть ряд вкладок над таблицей.
+3. Пройтись по вкладкам «На рассмотрении», «Отклоненные», «Заблокированные», «Все».</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Вкладки: «Все», «На рассмотрении», «Активные», «Отклоненные», «Заблокированные». «На рассмотрении» показывает только водителей, ожидающих проверки; «Отклоненные» — только отклонённых; «Заблокированные» — заблокированных; «Все» — всех. Переключение вкладки обновляет и счётчик записей.</t>
+        </is>
+      </c>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>web|positive|state</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>WEB-SA-067</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Web — Супер-администратор</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>/super-admin/partners/drivers</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>«Активные» — это проверенные: новый (PENDING) водитель туда не попадает</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Есть свежезарегистрированный водитель со статусом «на рассмотрении» (ещё не одобрен).</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>1. Открыть вкладку «Активные» и поискать этого водителя (в т.ч. поиском по ФИО/телефону).
+2. Открыть вкладку «На рассмотрении» и найти его там.</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Во вкладке «Активные» водителя НЕТ — вкладка фильтрует по статусу проверки «проверен», а не по признаку «не заблокирован». Во вкладке «На рассмотрении» водитель есть. (Регресс MNZL-265: ранее «Активные» показывала и непроверенных.)</t>
+        </is>
+      </c>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>web|negative|state</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>WEB-SA-068</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Web — Супер-администратор</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>/super-admin/partners/drivers/$id</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Карточка водителя «на рассмотрении»: чип статуса и кнопки решения</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Есть водитель со статусом «на рассмотрении».</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>1. Открыть карточку этого водителя из списка.
+2. Осмотреть шапку карточки.</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Рядом с ФИО — жёлтый чип «На рассмотрении» и чип активности. В шапке вместо кнопки «Редактировать» — две кнопки: зелёная «Согласовать» и красная контурная «Отклонить». В карточке виден паспорт (номер, введённый при регистрации).</t>
+        </is>
+      </c>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>web|positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>WEB-SA-069</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Web — Супер-администратор</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>/super-admin/partners/drivers/$id</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Согласование водителя через диалог подтверждения</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Открыта карточка водителя «на рассмотрении».</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>1. Нажать «Согласовать».
+2. Прочитать текст диалога.
+3. Подтвердить действие.
+4. Вернуться в список и открыть вкладку «Активные».</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Диалог: заголовок «Согласовать водителя?», текст «Заявка водителя «&lt;ФИО&gt;» будет согласована.». После подтверждения — тост «Водитель согласован», чип «На рассмотрении» исчезает (у проверенного чип статуса не показывается), вместо кнопок решения появляется «Редактировать». Водитель теперь во вкладке «Активные» и может подавать ставки в приложении.</t>
+        </is>
+      </c>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>web|positive|lifecycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>WEB-SA-070</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Web — Супер-администратор</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>/super-admin/partners/drivers/$id</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Отклонение водителя через диалог подтверждения</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Открыта карточка другого водителя «на рассмотрении».</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>1. Нажать «Отклонить».
+2. Подтвердить в диалоге «Отклонить водителя?» («Заявка водителя «&lt;ФИО&gt;» будет отклонена.»).
+3. Вернуться в список, открыть вкладку «Отклоненные».</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Тост «Водитель отклонён». В карточке — красный чип «Отклонён»; кнопок «Согласовать»/«Отклонить» больше нет (решение окончательное, обратно «на рассмотрение» не возвращают). Водитель отображается во вкладке «Отклоненные».</t>
+        </is>
+      </c>
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>web|positive|lifecycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>WEB-SA-071</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Web — Супер-администратор</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>/super-admin/partners/transport-companies</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Вкладки статуса проверки в списке транспортных компаний</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Есть самозарегистрированная ТК «на рассмотрении» (создана регистрацией через мобильный API).</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>1. Открыть «Партнёры → Транспортные компании».
+2. Пройтись по вкладкам «На рассмотрении», «Активные», «Отклоненные».</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Вкладки те же, что у водителей: «Все», «На рассмотрении», «Активные», «Отклоненные», «Заблокированные». Новая ТК видна в «На рассмотрении» с данными регистрации (название, ИНН); в «Активные» не попадает до одобрения.</t>
+        </is>
+      </c>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>web|positive|state</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>WEB-SA-072</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Web — Супер-администратор</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>/super-admin/partners/transport-companies/$id</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Согласование/отклонение транспортной компании из карточки</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Открыта карточка ТК «на рассмотрении».</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>1. Убедиться: рядом с названием чип «На рассмотрении», в шапке кнопки «Согласовать» и «Отклонить»; в карточке видны ИНН и юр. адрес из регистрации.
+2. Нажать «Согласовать», подтвердить в диалоге «Согласовать компанию?» («Заявка компании «&lt;название&gt;» будет согласована.»).
+3. Для другой ТК — «Отклонить» и подтвердить.</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Согласование: тост «Компания согласована», чип исчезает (у проверенной чип не показывается), ТК во вкладке «Активные» — её админ может подавать офферы. Отклонение: тост «Компания отклонена», красный чип «Отклонена», ТК во вкладке «Отклоненные».</t>
+        </is>
+      </c>
+      <c r="H72" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>web|positive|lifecycle</t>
         </is>
       </c>
     </row>

--- a/docs/testcases/manzil-web-testcases.xlsx
+++ b/docs/testcases/manzil-web-testcases.xlsx
@@ -2549,7 +2549,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Показывается страница «не найдено», а не пустой экран и не бесконечная загрузка.</t>
+          <t>Показывается страница «не найдено» (не пустой экран, не бесконечная загрузка). Уточнено по факту 2026-07-24: текст английский «Sorry, page not found!» — не локализован (→ BUG-041). Тест проверяет язык-независимо (URL остаётся + видимый текст page-not-found).</t>
         </is>
       </c>
       <c r="H38" s="9" t="inlineStr">
@@ -2560,7 +2560,7 @@
       <c r="I38" s="3" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>web|navigation</t>
+          <t>web|navigation (→ BUG-041: 404 не локализован)</t>
         </is>
       </c>
     </row>
